--- a/SGC-CKN/Excel/09baa496-3a43-473c-8014-b48e28d7f283_Hạng_mục_Lô_CT-02_P11-141_D800_22-03-2026.xlsx
+++ b/SGC-CKN/Excel/09baa496-3a43-473c-8014-b48e28d7f283_Hạng_mục_Lô_CT-02_P11-141_D800_22-03-2026.xlsx
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">05:10
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>2 Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám nâu, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">05:40
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>3 Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">07:00
@@ -133,50 +133,50 @@
 22/03/2026</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>7 Sét- đồi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét - đôi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">09:20
 22/03/2026</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>11 Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">10:20
 22/03/2026</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>12 Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
   </si>
   <si>
     <t xml:space="preserve">11:30
 22/03/2026</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>13 Cát pha, xám vàng, xám ghi TT dẻo; 14 Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, KC chặt vừa lẫn hỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">17:02
 22/03/2026</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>16 Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">18:22
